--- a/data/19_de_agosto.xlsx
+++ b/data/19_de_agosto.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,30 +462,45 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -510,24 +525,33 @@
         <v>23</v>
       </c>
       <c r="F2" t="n">
+        <v>22</v>
+      </c>
+      <c r="G2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
         <v>7</v>
       </c>
-      <c r="H2" t="n">
+      <c r="K2" t="n">
         <v>13</v>
       </c>
-      <c r="I2" t="n">
+      <c r="L2" t="n">
         <v>17</v>
       </c>
-      <c r="J2" t="n">
+      <c r="M2" t="n">
         <v>15</v>
       </c>
-      <c r="K2" t="n">
+      <c r="N2" t="n">
         <v>17</v>
       </c>
-      <c r="L2" t="n">
+      <c r="O2" t="n">
         <v>11</v>
       </c>
     </row>
@@ -553,21 +577,30 @@
         <v>21</v>
       </c>
       <c r="G3" t="n">
+        <v>15</v>
+      </c>
+      <c r="H3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I3" t="n">
+        <v>18</v>
+      </c>
+      <c r="J3" t="n">
         <v>11</v>
       </c>
-      <c r="H3" t="n">
-        <v>14</v>
-      </c>
-      <c r="I3" t="n">
-        <v>14</v>
-      </c>
-      <c r="J3" t="n">
-        <v>14</v>
-      </c>
       <c r="K3" t="n">
+        <v>14</v>
+      </c>
+      <c r="L3" t="n">
+        <v>14</v>
+      </c>
+      <c r="M3" t="n">
+        <v>14</v>
+      </c>
+      <c r="N3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
+      <c r="O3" t="n">
         <v>21</v>
       </c>
     </row>
@@ -590,24 +623,33 @@
         <v>16</v>
       </c>
       <c r="F4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H4" t="n">
+        <v>14</v>
+      </c>
+      <c r="I4" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
         <v>7</v>
       </c>
-      <c r="H4" t="n">
+      <c r="K4" t="n">
         <v>10</v>
       </c>
-      <c r="I4" t="n">
-        <v>14</v>
-      </c>
-      <c r="J4" t="n">
-        <v>14</v>
-      </c>
-      <c r="K4" t="n">
-        <v>14</v>
-      </c>
       <c r="L4" t="n">
+        <v>14</v>
+      </c>
+      <c r="M4" t="n">
+        <v>14</v>
+      </c>
+      <c r="N4" t="n">
+        <v>14</v>
+      </c>
+      <c r="O4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -633,21 +675,30 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
+        <v>19</v>
+      </c>
+      <c r="H5" t="n">
+        <v>40</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>10</v>
       </c>
-      <c r="H5" t="n">
+      <c r="K5" t="n">
         <v>21</v>
       </c>
-      <c r="I5" t="n">
+      <c r="L5" t="n">
         <v>16</v>
       </c>
-      <c r="J5" t="n">
+      <c r="M5" t="n">
         <v>15</v>
       </c>
-      <c r="K5" t="n">
+      <c r="N5" t="n">
         <v>10</v>
       </c>
-      <c r="L5" t="n">
+      <c r="O5" t="n">
         <v>24</v>
       </c>
     </row>
@@ -670,26 +721,35 @@
         <v>16</v>
       </c>
       <c r="F6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H6" t="n">
+        <v>14</v>
+      </c>
+      <c r="I6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
         <v>10</v>
       </c>
-      <c r="H6" t="n">
+      <c r="K6" t="n">
         <v>11</v>
-      </c>
-      <c r="I6" t="n">
-        <v>15</v>
-      </c>
-      <c r="J6" t="n">
-        <v>14</v>
-      </c>
-      <c r="K6" t="n">
-        <v>14</v>
       </c>
       <c r="L6" t="n">
         <v>15</v>
       </c>
+      <c r="M6" t="n">
+        <v>14</v>
+      </c>
+      <c r="N6" t="n">
+        <v>14</v>
+      </c>
+      <c r="O6" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -710,24 +770,33 @@
         <v>28</v>
       </c>
       <c r="F7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H7" t="n">
+        <v>28</v>
+      </c>
+      <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="n">
-        <v>14</v>
-      </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
+        <v>14</v>
+      </c>
+      <c r="L7" t="n">
         <v>21</v>
       </c>
-      <c r="J7" t="n">
+      <c r="M7" t="n">
         <v>21</v>
       </c>
-      <c r="K7" t="n">
+      <c r="N7" t="n">
         <v>19</v>
       </c>
-      <c r="L7" t="n">
+      <c r="O7" t="n">
         <v>27</v>
       </c>
     </row>
@@ -750,24 +819,33 @@
         <v>16</v>
       </c>
       <c r="F8" t="n">
+        <v>14</v>
+      </c>
+      <c r="G8" t="n">
+        <v>14</v>
+      </c>
+      <c r="H8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="G8" t="n">
+      <c r="J8" t="n">
         <v>9</v>
       </c>
-      <c r="H8" t="n">
+      <c r="K8" t="n">
         <v>10</v>
       </c>
-      <c r="I8" t="n">
-        <v>14</v>
-      </c>
-      <c r="J8" t="n">
-        <v>14</v>
-      </c>
-      <c r="K8" t="n">
-        <v>14</v>
-      </c>
       <c r="L8" t="n">
+        <v>14</v>
+      </c>
+      <c r="M8" t="n">
+        <v>14</v>
+      </c>
+      <c r="N8" t="n">
+        <v>14</v>
+      </c>
+      <c r="O8" t="n">
         <v>15</v>
       </c>
     </row>
@@ -790,24 +868,33 @@
         <v>19</v>
       </c>
       <c r="F9" t="n">
+        <v>14</v>
+      </c>
+      <c r="G9" t="n">
+        <v>15</v>
+      </c>
+      <c r="H9" t="n">
+        <v>19</v>
+      </c>
+      <c r="I9" t="n">
         <v>0</v>
       </c>
-      <c r="G9" t="n">
+      <c r="J9" t="n">
         <v>10</v>
       </c>
-      <c r="H9" t="n">
+      <c r="K9" t="n">
         <v>13</v>
       </c>
-      <c r="I9" t="n">
+      <c r="L9" t="n">
         <v>15</v>
       </c>
-      <c r="J9" t="n">
+      <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="n">
+      <c r="N9" t="n">
         <v>30</v>
       </c>
-      <c r="L9" t="n">
+      <c r="O9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -830,24 +917,33 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" t="n">
+        <v>19</v>
+      </c>
+      <c r="I10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" t="n">
         <v>7</v>
       </c>
-      <c r="H10" t="n">
+      <c r="K10" t="n">
         <v>13</v>
       </c>
-      <c r="I10" t="n">
+      <c r="L10" t="n">
         <v>16</v>
       </c>
-      <c r="J10" t="n">
+      <c r="M10" t="n">
         <v>15</v>
       </c>
-      <c r="K10" t="n">
+      <c r="N10" t="n">
         <v>18</v>
       </c>
-      <c r="L10" t="n">
+      <c r="O10" t="n">
         <v>11</v>
       </c>
     </row>
@@ -870,24 +966,33 @@
         <v>23</v>
       </c>
       <c r="F11" t="n">
+        <v>22</v>
+      </c>
+      <c r="G11" t="n">
+        <v>23</v>
+      </c>
+      <c r="H11" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" t="n">
         <v>0</v>
       </c>
-      <c r="G11" t="n">
+      <c r="J11" t="n">
         <v>7</v>
       </c>
-      <c r="H11" t="n">
+      <c r="K11" t="n">
         <v>13</v>
       </c>
-      <c r="I11" t="n">
+      <c r="L11" t="n">
         <v>18</v>
       </c>
-      <c r="J11" t="n">
-        <v>14</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
+        <v>14</v>
+      </c>
+      <c r="N11" t="n">
         <v>17</v>
       </c>
-      <c r="L11" t="n">
+      <c r="O11" t="n">
         <v>11</v>
       </c>
     </row>
@@ -902,7 +1007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -938,30 +1043,45 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -989,33 +1109,48 @@
           <t>23</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1050,26 +1185,41 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1101,33 +1251,48 @@
           <t>16</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1162,30 +1327,41 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -1217,33 +1393,48 @@
           <t>16</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1275,29 +1466,44 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -1329,33 +1535,48 @@
           <t>16</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="L8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1383,29 +1604,44 @@
           <t>19</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1437,33 +1673,52 @@
           <t>23</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1495,33 +1750,48 @@
           <t>23</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>11</t>
         </is>

--- a/data/19_de_agosto.xlsx
+++ b/data/19_de_agosto.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,30 +477,35 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -537,21 +542,24 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
+        <v>33</v>
+      </c>
+      <c r="K2" t="n">
         <v>7</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>13</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>17</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>15</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>17</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>11</v>
       </c>
     </row>
@@ -583,14 +591,14 @@
         <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>11</v>
       </c>
-      <c r="K3" t="n">
-        <v>14</v>
-      </c>
       <c r="L3" t="n">
         <v>14</v>
       </c>
@@ -598,9 +606,12 @@
         <v>14</v>
       </c>
       <c r="N3" t="n">
+        <v>14</v>
+      </c>
+      <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>21</v>
       </c>
     </row>
@@ -632,17 +643,17 @@
         <v>14</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K4" t="n">
         <v>7</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>10</v>
       </c>
-      <c r="L4" t="n">
-        <v>14</v>
-      </c>
       <c r="M4" t="n">
         <v>14</v>
       </c>
@@ -650,6 +661,9 @@
         <v>14</v>
       </c>
       <c r="O4" t="n">
+        <v>14</v>
+      </c>
+      <c r="P4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -684,21 +698,24 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>38</v>
+      </c>
+      <c r="K5" t="n">
         <v>10</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>21</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>16</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>15</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>10</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>24</v>
       </c>
     </row>
@@ -730,24 +747,27 @@
         <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J6" t="n">
+        <v>14</v>
+      </c>
+      <c r="K6" t="n">
         <v>10</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>11</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>15</v>
       </c>
-      <c r="M6" t="n">
-        <v>14</v>
-      </c>
       <c r="N6" t="n">
         <v>14</v>
       </c>
       <c r="O6" t="n">
+        <v>14</v>
+      </c>
+      <c r="P6" t="n">
         <v>15</v>
       </c>
     </row>
@@ -782,21 +802,24 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
+        <v>42</v>
+      </c>
+      <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="n">
-        <v>14</v>
-      </c>
       <c r="L7" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="M7" t="n">
         <v>21</v>
       </c>
       <c r="N7" t="n">
+        <v>21</v>
+      </c>
+      <c r="O7" t="n">
         <v>19</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>27</v>
       </c>
     </row>
@@ -828,17 +851,17 @@
         <v>13</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J8" t="n">
+        <v>14</v>
+      </c>
+      <c r="K8" t="n">
         <v>9</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>10</v>
       </c>
-      <c r="L8" t="n">
-        <v>14</v>
-      </c>
       <c r="M8" t="n">
         <v>14</v>
       </c>
@@ -846,6 +869,9 @@
         <v>14</v>
       </c>
       <c r="O8" t="n">
+        <v>14</v>
+      </c>
+      <c r="P8" t="n">
         <v>15</v>
       </c>
     </row>
@@ -877,24 +903,27 @@
         <v>19</v>
       </c>
       <c r="I9" t="n">
+        <v>17</v>
+      </c>
+      <c r="J9" t="n">
+        <v>16</v>
+      </c>
+      <c r="K9" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" t="n">
+        <v>13</v>
+      </c>
+      <c r="M9" t="n">
+        <v>15</v>
+      </c>
+      <c r="N9" t="n">
         <v>0</v>
       </c>
-      <c r="J9" t="n">
-        <v>10</v>
-      </c>
-      <c r="K9" t="n">
-        <v>13</v>
-      </c>
-      <c r="L9" t="n">
-        <v>15</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>30</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -926,24 +955,27 @@
         <v>19</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J10" t="n">
+        <v>12</v>
+      </c>
+      <c r="K10" t="n">
         <v>7</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>13</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>16</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>15</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>18</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11</v>
       </c>
     </row>
@@ -975,24 +1007,27 @@
         <v>10</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J11" t="n">
+        <v>12</v>
+      </c>
+      <c r="K11" t="n">
         <v>7</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>13</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>18</v>
       </c>
-      <c r="M11" t="n">
-        <v>14</v>
-      </c>
       <c r="N11" t="n">
+        <v>14</v>
+      </c>
+      <c r="O11" t="n">
         <v>17</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1007,7 +1042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1058,30 +1093,35 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1127,30 +1167,35 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1195,19 +1240,15 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>14</t>
@@ -1218,8 +1259,13 @@
           <t>14</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1266,22 +1312,26 @@
           <t>14</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>14</t>
@@ -1293,6 +1343,11 @@
         </is>
       </c>
       <c r="O4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1338,30 +1393,35 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -1408,33 +1468,42 @@
           <t>14</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1482,28 +1551,33 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -1550,22 +1624,26 @@
           <t>13</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>14</t>
@@ -1577,6 +1655,11 @@
         </is>
       </c>
       <c r="O8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1619,29 +1702,38 @@
           <t>19</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1690,35 +1782,40 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1765,33 +1862,42 @@
           <t>10</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>11</t>
         </is>

--- a/data/19_de_agosto.xlsx
+++ b/data/19_de_agosto.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,30 +482,35 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -545,21 +550,24 @@
         <v>33</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>7</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>13</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>17</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>15</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>17</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>11</v>
       </c>
     </row>
@@ -597,11 +605,11 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
+        <v>30</v>
+      </c>
+      <c r="L3" t="n">
         <v>11</v>
       </c>
-      <c r="L3" t="n">
-        <v>14</v>
-      </c>
       <c r="M3" t="n">
         <v>14</v>
       </c>
@@ -609,9 +617,12 @@
         <v>14</v>
       </c>
       <c r="O3" t="n">
+        <v>14</v>
+      </c>
+      <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>21</v>
       </c>
     </row>
@@ -649,14 +660,14 @@
         <v>14</v>
       </c>
       <c r="K4" t="n">
+        <v>14</v>
+      </c>
+      <c r="L4" t="n">
         <v>7</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>10</v>
       </c>
-      <c r="M4" t="n">
-        <v>14</v>
-      </c>
       <c r="N4" t="n">
         <v>14</v>
       </c>
@@ -664,6 +675,9 @@
         <v>14</v>
       </c>
       <c r="P4" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -701,21 +715,24 @@
         <v>38</v>
       </c>
       <c r="K5" t="n">
+        <v>13</v>
+      </c>
+      <c r="L5" t="n">
         <v>10</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>21</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>16</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>15</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>10</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>24</v>
       </c>
     </row>
@@ -753,21 +770,24 @@
         <v>14</v>
       </c>
       <c r="K6" t="n">
+        <v>14</v>
+      </c>
+      <c r="L6" t="n">
         <v>10</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>11</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>15</v>
       </c>
-      <c r="N6" t="n">
-        <v>14</v>
-      </c>
       <c r="O6" t="n">
         <v>14</v>
       </c>
       <c r="P6" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q6" t="n">
         <v>15</v>
       </c>
     </row>
@@ -805,21 +825,24 @@
         <v>42</v>
       </c>
       <c r="K7" t="n">
+        <v>21</v>
+      </c>
+      <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="n">
-        <v>14</v>
-      </c>
       <c r="M7" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="N7" t="n">
         <v>21</v>
       </c>
       <c r="O7" t="n">
+        <v>21</v>
+      </c>
+      <c r="P7" t="n">
         <v>19</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>27</v>
       </c>
     </row>
@@ -857,14 +880,14 @@
         <v>14</v>
       </c>
       <c r="K8" t="n">
+        <v>14</v>
+      </c>
+      <c r="L8" t="n">
         <v>9</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>10</v>
       </c>
-      <c r="M8" t="n">
-        <v>14</v>
-      </c>
       <c r="N8" t="n">
         <v>14</v>
       </c>
@@ -872,6 +895,9 @@
         <v>14</v>
       </c>
       <c r="P8" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q8" t="n">
         <v>15</v>
       </c>
     </row>
@@ -909,21 +935,24 @@
         <v>16</v>
       </c>
       <c r="K9" t="n">
+        <v>14</v>
+      </c>
+      <c r="L9" t="n">
         <v>10</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>13</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>15</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>30</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -961,21 +990,24 @@
         <v>12</v>
       </c>
       <c r="K10" t="n">
+        <v>14</v>
+      </c>
+      <c r="L10" t="n">
         <v>7</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>13</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>16</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>15</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>18</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1013,21 +1045,24 @@
         <v>12</v>
       </c>
       <c r="K11" t="n">
+        <v>13</v>
+      </c>
+      <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>13</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>18</v>
       </c>
-      <c r="N11" t="n">
-        <v>14</v>
-      </c>
       <c r="O11" t="n">
+        <v>14</v>
+      </c>
+      <c r="P11" t="n">
         <v>17</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1042,7 +1077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,30 +1133,35 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1170,32 +1210,33 @@
           <t>33</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1246,14 +1287,14 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>14</t>
@@ -1264,8 +1305,13 @@
           <t>14</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1324,19 +1370,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>14</t>
@@ -1348,6 +1394,11 @@
         </is>
       </c>
       <c r="P4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1398,30 +1449,35 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -1480,30 +1536,35 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1556,28 +1617,33 @@
           <t>42</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -1636,19 +1702,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>14</t>
@@ -1660,6 +1726,11 @@
         </is>
       </c>
       <c r="P8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1714,26 +1785,31 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1792,30 +1868,35 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1874,30 +1955,35 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="O11" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>11</t>
         </is>

--- a/data/19_de_agosto.xlsx
+++ b/data/19_de_agosto.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,30 +487,35 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -553,21 +558,24 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>24</v>
+      </c>
+      <c r="M2" t="n">
         <v>7</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>13</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>17</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>15</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>17</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>11</v>
       </c>
     </row>
@@ -608,11 +616,11 @@
         <v>30</v>
       </c>
       <c r="L3" t="n">
+        <v>7</v>
+      </c>
+      <c r="M3" t="n">
         <v>11</v>
       </c>
-      <c r="M3" t="n">
-        <v>14</v>
-      </c>
       <c r="N3" t="n">
         <v>14</v>
       </c>
@@ -620,9 +628,12 @@
         <v>14</v>
       </c>
       <c r="P3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>21</v>
       </c>
     </row>
@@ -663,14 +674,14 @@
         <v>14</v>
       </c>
       <c r="L4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M4" t="n">
         <v>7</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>10</v>
       </c>
-      <c r="N4" t="n">
-        <v>14</v>
-      </c>
       <c r="O4" t="n">
         <v>14</v>
       </c>
@@ -678,6 +689,9 @@
         <v>14</v>
       </c>
       <c r="Q4" t="n">
+        <v>14</v>
+      </c>
+      <c r="R4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -718,21 +732,24 @@
         <v>13</v>
       </c>
       <c r="L5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M5" t="n">
         <v>10</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>21</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>16</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>15</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>10</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>24</v>
       </c>
     </row>
@@ -776,18 +793,21 @@
         <v>10</v>
       </c>
       <c r="M6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N6" t="n">
         <v>11</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>15</v>
       </c>
-      <c r="O6" t="n">
-        <v>14</v>
-      </c>
       <c r="P6" t="n">
         <v>14</v>
       </c>
       <c r="Q6" t="n">
+        <v>14</v>
+      </c>
+      <c r="R6" t="n">
         <v>15</v>
       </c>
     </row>
@@ -828,21 +848,24 @@
         <v>21</v>
       </c>
       <c r="L7" t="n">
+        <v>14</v>
+      </c>
+      <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="M7" t="n">
-        <v>14</v>
-      </c>
       <c r="N7" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="O7" t="n">
         <v>21</v>
       </c>
       <c r="P7" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q7" t="n">
         <v>19</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>27</v>
       </c>
     </row>
@@ -883,14 +906,14 @@
         <v>14</v>
       </c>
       <c r="L8" t="n">
+        <v>10</v>
+      </c>
+      <c r="M8" t="n">
         <v>9</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>10</v>
       </c>
-      <c r="N8" t="n">
-        <v>14</v>
-      </c>
       <c r="O8" t="n">
         <v>14</v>
       </c>
@@ -898,6 +921,9 @@
         <v>14</v>
       </c>
       <c r="Q8" t="n">
+        <v>14</v>
+      </c>
+      <c r="R8" t="n">
         <v>15</v>
       </c>
     </row>
@@ -938,21 +964,24 @@
         <v>14</v>
       </c>
       <c r="L9" t="n">
+        <v>7</v>
+      </c>
+      <c r="M9" t="n">
         <v>10</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>13</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>15</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>0</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>30</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -993,21 +1022,24 @@
         <v>14</v>
       </c>
       <c r="L10" t="n">
+        <v>22</v>
+      </c>
+      <c r="M10" t="n">
         <v>7</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>13</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>16</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>15</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>18</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1048,21 +1080,24 @@
         <v>13</v>
       </c>
       <c r="L11" t="n">
+        <v>9</v>
+      </c>
+      <c r="M11" t="n">
         <v>7</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>13</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>18</v>
       </c>
-      <c r="O11" t="n">
-        <v>14</v>
-      </c>
       <c r="P11" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q11" t="n">
         <v>17</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1077,7 +1112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1138,30 +1173,35 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1213,30 +1253,35 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1292,14 +1337,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>14</t>
@@ -1310,8 +1355,13 @@
           <t>14</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1375,19 +1425,19 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="O4" t="inlineStr">
         <is>
           <t>14</t>
@@ -1399,6 +1449,11 @@
         </is>
       </c>
       <c r="Q4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1454,30 +1509,35 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -1546,25 +1606,30 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1622,28 +1687,33 @@
           <t>21</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -1707,19 +1777,19 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>14</t>
@@ -1731,6 +1801,11 @@
         </is>
       </c>
       <c r="Q8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1790,26 +1865,31 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1873,30 +1953,35 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1960,30 +2045,35 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>11</t>
         </is>

--- a/data/19_de_agosto.xlsx
+++ b/data/19_de_agosto.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,30 +492,50 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>15dec2025</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -561,21 +581,33 @@
         <v>24</v>
       </c>
       <c r="M2" t="n">
+        <v>15</v>
+      </c>
+      <c r="N2" t="n">
+        <v>15</v>
+      </c>
+      <c r="O2" t="n">
+        <v>14</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>7</v>
       </c>
-      <c r="N2" t="n">
+      <c r="R2" t="n">
         <v>13</v>
       </c>
-      <c r="O2" t="n">
+      <c r="S2" t="n">
         <v>17</v>
       </c>
-      <c r="P2" t="n">
+      <c r="T2" t="n">
         <v>15</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="U2" t="n">
         <v>17</v>
       </c>
-      <c r="R2" t="n">
+      <c r="V2" t="n">
         <v>11</v>
       </c>
     </row>
@@ -619,21 +651,33 @@
         <v>7</v>
       </c>
       <c r="M3" t="n">
+        <v>16</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>16</v>
+      </c>
+      <c r="P3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q3" t="n">
         <v>11</v>
       </c>
-      <c r="N3" t="n">
-        <v>14</v>
-      </c>
-      <c r="O3" t="n">
-        <v>14</v>
-      </c>
-      <c r="P3" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
+        <v>14</v>
+      </c>
+      <c r="S3" t="n">
+        <v>14</v>
+      </c>
+      <c r="T3" t="n">
+        <v>14</v>
+      </c>
+      <c r="U3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="n">
+      <c r="V3" t="n">
         <v>21</v>
       </c>
     </row>
@@ -677,21 +721,33 @@
         <v>10</v>
       </c>
       <c r="M4" t="n">
+        <v>13</v>
+      </c>
+      <c r="N4" t="n">
+        <v>11</v>
+      </c>
+      <c r="O4" t="n">
+        <v>13</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>7</v>
       </c>
-      <c r="N4" t="n">
+      <c r="R4" t="n">
         <v>10</v>
       </c>
-      <c r="O4" t="n">
-        <v>14</v>
-      </c>
-      <c r="P4" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>14</v>
-      </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
+        <v>14</v>
+      </c>
+      <c r="T4" t="n">
+        <v>14</v>
+      </c>
+      <c r="U4" t="n">
+        <v>14</v>
+      </c>
+      <c r="V4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -735,21 +791,33 @@
         <v>12</v>
       </c>
       <c r="M5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="O5" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>10</v>
       </c>
       <c r="R5" t="n">
+        <v>21</v>
+      </c>
+      <c r="S5" t="n">
+        <v>16</v>
+      </c>
+      <c r="T5" t="n">
+        <v>15</v>
+      </c>
+      <c r="U5" t="n">
+        <v>10</v>
+      </c>
+      <c r="V5" t="n">
         <v>24</v>
       </c>
     </row>
@@ -793,21 +861,33 @@
         <v>10</v>
       </c>
       <c r="M6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N6" t="n">
         <v>11</v>
       </c>
       <c r="O6" t="n">
+        <v>12</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>10</v>
+      </c>
+      <c r="R6" t="n">
+        <v>11</v>
+      </c>
+      <c r="S6" t="n">
         <v>15</v>
       </c>
-      <c r="P6" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>14</v>
-      </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
+        <v>14</v>
+      </c>
+      <c r="U6" t="n">
+        <v>14</v>
+      </c>
+      <c r="V6" t="n">
         <v>15</v>
       </c>
     </row>
@@ -851,21 +931,33 @@
         <v>14</v>
       </c>
       <c r="M7" t="n">
+        <v>21</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20</v>
+      </c>
+      <c r="O7" t="n">
+        <v>16</v>
+      </c>
+      <c r="P7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="n">
-        <v>14</v>
-      </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>14</v>
+      </c>
+      <c r="S7" t="n">
         <v>21</v>
       </c>
-      <c r="P7" t="n">
+      <c r="T7" t="n">
         <v>21</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="U7" t="n">
         <v>19</v>
       </c>
-      <c r="R7" t="n">
+      <c r="V7" t="n">
         <v>27</v>
       </c>
     </row>
@@ -909,21 +1001,33 @@
         <v>10</v>
       </c>
       <c r="M8" t="n">
+        <v>13</v>
+      </c>
+      <c r="N8" t="n">
+        <v>12</v>
+      </c>
+      <c r="O8" t="n">
+        <v>13</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>9</v>
       </c>
-      <c r="N8" t="n">
+      <c r="R8" t="n">
         <v>10</v>
       </c>
-      <c r="O8" t="n">
-        <v>14</v>
-      </c>
-      <c r="P8" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>14</v>
-      </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
+        <v>14</v>
+      </c>
+      <c r="T8" t="n">
+        <v>14</v>
+      </c>
+      <c r="U8" t="n">
+        <v>14</v>
+      </c>
+      <c r="V8" t="n">
         <v>15</v>
       </c>
     </row>
@@ -967,21 +1071,33 @@
         <v>7</v>
       </c>
       <c r="M9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="N9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
+        <v>10</v>
+      </c>
+      <c r="R9" t="n">
+        <v>13</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
         <v>30</v>
       </c>
-      <c r="R9" t="n">
+      <c r="V9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1025,21 +1141,33 @@
         <v>22</v>
       </c>
       <c r="M10" t="n">
+        <v>17</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>20</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>7</v>
       </c>
-      <c r="N10" t="n">
+      <c r="R10" t="n">
         <v>13</v>
       </c>
-      <c r="O10" t="n">
+      <c r="S10" t="n">
         <v>16</v>
       </c>
-      <c r="P10" t="n">
+      <c r="T10" t="n">
         <v>15</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="U10" t="n">
         <v>18</v>
       </c>
-      <c r="R10" t="n">
+      <c r="V10" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1083,21 +1211,33 @@
         <v>9</v>
       </c>
       <c r="M11" t="n">
+        <v>17</v>
+      </c>
+      <c r="N11" t="n">
+        <v>15</v>
+      </c>
+      <c r="O11" t="n">
+        <v>14</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>7</v>
       </c>
-      <c r="N11" t="n">
+      <c r="R11" t="n">
         <v>13</v>
       </c>
-      <c r="O11" t="n">
+      <c r="S11" t="n">
         <v>18</v>
       </c>
-      <c r="P11" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="T11" t="n">
+        <v>14</v>
+      </c>
+      <c r="U11" t="n">
         <v>17</v>
       </c>
-      <c r="R11" t="n">
+      <c r="V11" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1112,7 +1252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1178,30 +1318,50 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>15dec2025</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1258,30 +1418,46 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1342,26 +1518,42 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1430,30 +1622,46 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1512,32 +1720,40 @@
           <t>12</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -1606,30 +1822,46 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1692,28 +1924,44 @@
           <t>14</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -1782,30 +2030,46 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1870,26 +2134,42 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1958,30 +2238,46 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -2050,30 +2346,46 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>11</t>
         </is>

--- a/data/19_de_agosto.xlsx
+++ b/data/19_de_agosto.xlsx
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q5" t="n">
         <v>10</v>
@@ -940,7 +940,7 @@
         <v>16</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1727,7 +1727,11 @@
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>10</t>
@@ -1939,7 +1943,11 @@
           <t>16</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
